--- a/lucas/import_data/utility/observation/excel/indicator.xlsx
+++ b/lucas/import_data/utility/observation/excel/indicator.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="228">
   <si>
     <t xml:space="preserve">quantity_id__quantity_name</t>
   </si>
@@ -674,6 +674,36 @@
   </si>
   <si>
     <t xml:space="preserve">Bacteria relative microbial content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classification with nominative value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture class iuss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture iuss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soil texture class IUSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IUSS soil texture classification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture class usda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil textur usda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soil texture class USDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USDA soil texture classification</t>
   </si>
 </sst>
 </file>
@@ -683,7 +713,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -704,11 +734,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -767,7 +792,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -776,19 +801,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -872,37 +893,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -975,8 +996,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E93"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.26"/>
@@ -1200,30 +1221,30 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1332,7 +1353,7 @@
       <c r="B25" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D25" s="1" t="s">
@@ -1503,7 +1524,7 @@
       <c r="C37" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="2" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1564,7 +1585,7 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="2" t="s">
         <v>99</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -1578,7 +1599,7 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="2" t="s">
         <v>99</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -1592,7 +1613,7 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -1606,7 +1627,7 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -1620,7 +1641,7 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -1634,7 +1655,7 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -1648,7 +1669,7 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -1662,7 +1683,7 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -1676,7 +1697,7 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B50" s="1" t="s">
@@ -1690,7 +1711,7 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="2" t="s">
         <v>99</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -1704,7 +1725,7 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="2" t="s">
         <v>99</v>
       </c>
       <c r="B52" s="1" t="s">
@@ -1718,7 +1739,7 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B53" s="1" t="s">
@@ -1732,7 +1753,7 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B54" s="1" t="s">
@@ -1746,7 +1767,7 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -1760,7 +1781,7 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B56" s="1" t="s">
@@ -1774,58 +1795,58 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="2" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="2" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="2" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D60" s="2" t="s">
         <v>140</v>
       </c>
     </row>
@@ -1833,7 +1854,7 @@
       <c r="A61" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" s="4" t="s">
         <v>142</v>
       </c>
       <c r="C61" s="1" t="s">
@@ -1847,7 +1868,7 @@
       <c r="A62" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="4" t="s">
         <v>145</v>
       </c>
       <c r="C62" s="1" t="s">
@@ -1861,7 +1882,7 @@
       <c r="A63" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B63" s="4" t="s">
         <v>148</v>
       </c>
       <c r="C63" s="1" t="s">
@@ -1875,7 +1896,7 @@
       <c r="A64" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B64" s="4" t="s">
         <v>151</v>
       </c>
       <c r="C64" s="1" t="s">
@@ -1889,7 +1910,7 @@
       <c r="A65" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="B65" s="4" t="s">
         <v>154</v>
       </c>
       <c r="C65" s="1" t="s">
@@ -1903,7 +1924,7 @@
       <c r="A66" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B66" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C66" s="1" t="s">
@@ -2012,7 +2033,7 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="2" t="s">
         <v>157</v>
       </c>
       <c r="B74" s="1" t="s">
@@ -2026,7 +2047,7 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="s">
+      <c r="A75" s="2" t="s">
         <v>157</v>
       </c>
       <c r="B75" s="1" t="s">
@@ -2040,7 +2061,7 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="2" t="s">
         <v>157</v>
       </c>
       <c r="B76" s="1" t="s">
@@ -2102,10 +2123,10 @@
       <c r="B80" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="C80" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D80" s="4" t="s">
+      <c r="D80" s="2" t="s">
         <v>183</v>
       </c>
     </row>
@@ -2152,10 +2173,10 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="4" t="s">
+      <c r="A84" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B84" s="2" t="s">
         <v>192</v>
       </c>
       <c r="C84" s="1" t="s">
@@ -2268,6 +2289,57 @@
       </c>
       <c r="E90" s="1" t="s">
         <v>217</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/lucas/import_data/utility/observation/excel/indicator.xlsx
+++ b/lucas/import_data/utility/observation/excel/indicator.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="237">
   <si>
     <t xml:space="preserve">quantity_id__quantity_name</t>
   </si>
@@ -697,13 +697,40 @@
     <t xml:space="preserve">soil texture class usda</t>
   </si>
   <si>
-    <t xml:space="preserve">soil textur usda</t>
+    <t xml:space="preserve">soil texture usda</t>
   </si>
   <si>
     <t xml:space="preserve">Soil texture class USDA</t>
   </si>
   <si>
     <t xml:space="preserve">USDA soil texture classification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture class usda major group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture usda major group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soil texture usda major group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture class iuss major group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture iuss major group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soil texture iuss major group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">compilation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compilation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compilation of 2 or more source datasets to a single dataset</t>
   </si>
 </sst>
 </file>
@@ -996,7 +1023,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.85"/>
@@ -2342,6 +2369,51 @@
         <v>227</v>
       </c>
     </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B12" r:id="rId1" display="soil cylinder drying@105c soil moisture volumetric content"/>

--- a/lucas/import_data/utility/observation/excel/indicator.xlsx
+++ b/lucas/import_data/utility/observation/excel/indicator.xlsx
@@ -76,10 +76,13 @@
     <t xml:space="preserve">sm</t>
   </si>
   <si>
-    <t xml:space="preserve">soil cylinder drying@105c soil moisture volumetric content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cylinder soil moisture</t>
+    <t xml:space="preserve">soil moisture volumetric content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil moisture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soil moisture volumetric content</t>
   </si>
   <si>
     <t xml:space="preserve">temp</t>
@@ -305,9 +308,6 @@
   </si>
   <si>
     <t xml:space="preserve">soil moisture content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soil moisture</t>
   </si>
   <si>
     <t xml:space="preserve">bulk density</t>
@@ -843,427 +843,427 @@
         <v>19</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="D12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D16" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="D17" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="D18" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="D19" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="D20" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="D21" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="D22" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="D23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="D24" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="D25" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="D26" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="D35" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="D36" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="D37" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="D38" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="D39" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1405,9 +1405,6 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B11" r:id="rId1" display="soil cylinder drying@105c soil moisture volumetric content"/>
-  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
